--- a/report/test_results_search.xlsx
+++ b/report/test_results_search.xlsx
@@ -1,132 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PythonProject1\report\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2471955C-82A8-4A0D-B017-446B203B9DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Results Search" sheetId="1" r:id="rId1"/>
+    <sheet name="Test Results Search" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>Test Name</t>
-  </si>
-  <si>
-    <t>Keyword</t>
-  </si>
-  <si>
-    <t>Expected</t>
-  </si>
-  <si>
-    <t>Actual</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>2025-09-26 23:37:34</t>
-  </si>
-  <si>
-    <t>test_search_'tee'</t>
-  </si>
-  <si>
-    <t>tee</t>
-  </si>
-  <si>
-    <t>Please fill out this field.</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>2025-09-26 23:37:43</t>
-  </si>
-  <si>
-    <t>test_search_'áo'</t>
-  </si>
-  <si>
-    <t>áo</t>
-  </si>
-  <si>
-    <t>2025-09-26 23:37:54</t>
-  </si>
-  <si>
-    <t>test_search_'123456'</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>2025-09-26 23:38:04</t>
-  </si>
-  <si>
-    <t>test_search_'#%$@%'</t>
-  </si>
-  <si>
-    <t>#%$@%</t>
-  </si>
-  <si>
-    <t>2025-09-26 23:38:13</t>
-  </si>
-  <si>
-    <t>test_search_'tê'</t>
-  </si>
-  <si>
-    <t>tê</t>
-  </si>
-  <si>
-    <t>2025-09-26 23:38:23</t>
-  </si>
-  <si>
-    <t>test_search_'     bag'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     bag</t>
-  </si>
-  <si>
-    <t>2025-09-26 23:38:35</t>
-  </si>
-  <si>
-    <t>test_search_''</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -160,24 +66,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -465,172 +430,806 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.21875" customWidth="1"/>
-    <col min="2" max="2" width="24.21875" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="25.6640625" customWidth="1"/>
-    <col min="5" max="5" width="27.44140625" customWidth="1"/>
+    <col width="18.21875" customWidth="1" min="1" max="1"/>
+    <col width="24.21875" customWidth="1" min="2" max="2"/>
+    <col width="16.6640625" customWidth="1" min="3" max="3"/>
+    <col width="25.6640625" customWidth="1" min="4" max="4"/>
+    <col width="27.44140625" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Test Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-09-26 23:37:34</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>test_search_'tee'</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-09-26 23:37:43</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>test_search_'áo'</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>áo</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-09-26 23:37:54</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>test_search_'123456'</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-09-26 23:38:04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>test_search_'#%$@%'</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>#%$@%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-09-26 23:38:13</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>test_search_'tê'</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>tê</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-09-26 23:38:23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>test_search_'     bag'</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     bag</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-09-26 23:38:35</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>test_search_''</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:32:58</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>search_tee</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Có 150 sản phẩm cho tìm kiếm</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:33:06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>search_áo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>áo</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Không tìm thấy nội dung bạn yêu cầu</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:35:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>search_tee</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Có 150 sản phẩm cho tìm kiếm</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:35:10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>search_áo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>áo</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Không tìm thấy nội dung bạn yêu cầu</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:38:38</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>search_tee</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Có 150 sản phẩm cho tìm kiếm</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:39:03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>search_áo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>áo</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Không tìm thấy nội dung bạn yêu cầu</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:39:29</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>search_123456</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Không tìm thấy nội dung bạn yêu cầu</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:39:54</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>search_#%$@%</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>#%$@%</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Không tìm thấy nội dung bạn yêu cầu</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:40:16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>search_tê</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>tê</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Có 150 sản phẩm cho tìm kiếm</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:40:41</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>search_bag</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Có 2 sản phẩm cho tìm kiếm</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:41:17</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>search_empty</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:41:44</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>search_SWE SPIKE BOXY TEE – WHITE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SWE SPIKE BOXY TEE – WHITE</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Có 1 sản phẩm cho tìm kiếm</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:45:52</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>search_tee</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>tee</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Có 150 sản phẩm cho tìm kiếm</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:46:17</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>search_áo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>áo</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Không tìm thấy "". Vui lòng kiểm tra chính tả</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:46:43</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>search_123456</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Không tìm thấy "123456". Vui lòng kiểm tra chính tả</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:47:08</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>search_#%$@%</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>#%$@%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Không tìm thấy "#%$@%". Vui lòng kiểm tra chính tả</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:47:28</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>search_tê</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>tê</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Có 150 sản phẩm cho tìm kiếm</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:47:49</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>search_bag</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Có 2 sản phẩm cho tìm kiếm</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:48:21</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>search_empty</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Please fill out this field.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:48:44</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>search_SWE SPIKE BOXY TEE – WHITE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SWE SPIKE BOXY TEE – WHITE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Có 1 sản phẩm cho tìm kiếm</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
       </c>
     </row>
   </sheetData>
